--- a/EDP_MARKET.xlsx
+++ b/EDP_MARKET.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Alunos" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="EDPs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Compras" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -83,19 +84,28 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="general" vertical="bottom"/>
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -358,53 +368,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="24.34" customWidth="1" style="4" min="2" max="2"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="2">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="5">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>Nome</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>EDP atribuído</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Etapa</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Orçamento inicial</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Saldo</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>Pontos</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="15" customHeight="1" s="2">
+    <row r="2" ht="15" customHeight="1" s="5">
       <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>Ana Beatriz Almeida</t>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>Agnes</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -422,13 +435,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="2">
+    <row r="3" ht="15" customHeight="1" s="5">
       <c r="A3" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Bruno Henrique Martins</t>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Ana Clara</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -446,13 +459,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" ht="15" customHeight="1" s="2">
+    <row r="4" ht="15" customHeight="1" s="5">
       <c r="A4" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Camila Rodrigues Souza</t>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>Ana Julia</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -470,13 +483,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="15" customHeight="1" s="2">
+    <row r="5" ht="15" customHeight="1" s="5">
       <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Carlos Eduardo Ferreira</t>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Bianca Azevedo</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -494,13 +507,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1" s="2">
+    <row r="6" ht="15" customHeight="1" s="5">
       <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>Daniela Alves Ribeiro</t>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -518,13 +531,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1" s="2">
+    <row r="7" ht="15" customHeight="1" s="5">
       <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Diego Matheus Costa</t>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>Bruna</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -542,13 +555,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="15" customHeight="1" s="2">
+    <row r="8" ht="15" customHeight="1" s="5">
       <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>Eduarda Lima Santos</t>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Caio</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -566,13 +579,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="15" customHeight="1" s="2">
+    <row r="9" ht="15" customHeight="1" s="5">
       <c r="A9" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Felipe Augusto Oliveira</t>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>Carolina</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -590,13 +603,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="15" customHeight="1" s="2">
+    <row r="10" ht="15" customHeight="1" s="5">
       <c r="A10" s="4" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>Fernanda Cristina Rocha</t>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>Caroline</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -614,13 +627,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="15" customHeight="1" s="2">
+    <row r="11" ht="15" customHeight="1" s="5">
       <c r="A11" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Gabriel Mendes Carvalho</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Diego</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -638,13 +651,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="15" customHeight="1" s="2">
+    <row r="12" ht="15" customHeight="1" s="5">
       <c r="A12" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>Giovanna Pereira Lima</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Erick</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -662,13 +675,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="15" customHeight="1" s="2">
+    <row r="13" ht="15" customHeight="1" s="5">
       <c r="A13" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Gustavo Henrique Barbosa</t>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Gabriella</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -686,13 +699,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="15" customHeight="1" s="2">
+    <row r="14" ht="15" customHeight="1" s="5">
       <c r="A14" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Helena Martins da Silva</t>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>Giulia</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -710,13 +723,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="15" customHeight="1" s="2">
+    <row r="15" ht="15" customHeight="1" s="5">
       <c r="A15" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Igor Rafael Nascimento</t>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>Guilherme</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -734,13 +747,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="15" customHeight="1" s="2">
+    <row r="16" ht="15" customHeight="1" s="5">
       <c r="A16" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Isabela Freitas Gomes</t>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>Gustavo Felicio</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -758,13 +771,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="15" customHeight="1" s="2">
+    <row r="17" ht="15" customHeight="1" s="5">
       <c r="A17" s="4" t="n">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>João Pedro Moreira</t>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>Gustavo Varela</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -782,13 +795,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1" s="2">
+    <row r="18" ht="15" customHeight="1" s="5">
       <c r="A18" s="4" t="n">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Júlia Fernandes Castro</t>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>Igor</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -806,13 +819,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1" s="2">
+    <row r="19" ht="15" customHeight="1" s="5">
       <c r="A19" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Leonardo Almeida Pinto</t>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>Jessica</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -830,13 +843,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1" s="2">
+    <row r="20" ht="15" customHeight="1" s="5">
       <c r="A20" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Letícia Vitória Cardoso</t>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Joao Batista</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -854,13 +867,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="15" customHeight="1" s="2">
+    <row r="21" ht="15" customHeight="1" s="5">
       <c r="A21" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Lucas Gabriel Teixeira</t>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Joao Paulo</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -878,13 +891,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="15" customHeight="1" s="2">
+    <row r="22" ht="15" customHeight="1" s="5">
       <c r="A22" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Mariana Alves Costa</t>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>Joao Pedro</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -902,13 +915,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="15" customHeight="1" s="2">
+    <row r="23" ht="15" customHeight="1" s="5">
       <c r="A23" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Matheus Rodrigues Pereira</t>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Jorge</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -926,13 +939,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="15" customHeight="1" s="2">
+    <row r="24" ht="15" customHeight="1" s="5">
       <c r="A24" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Mayara Cristina Lopes</t>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>Kassiane</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
@@ -950,13 +963,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="15" customHeight="1" s="2">
+    <row r="25" ht="15" customHeight="1" s="5">
       <c r="A25" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Miguel Ângelo Santos</t>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -974,13 +987,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="15" customHeight="1" s="2">
+    <row r="26" ht="15" customHeight="1" s="5">
       <c r="A26" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Natália Ferreira Mendes</t>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>Laura</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -998,13 +1011,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="15" customHeight="1" s="2">
+    <row r="27" ht="15" customHeight="1" s="5">
       <c r="A27" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Nicolas Duarte Ribeiro</t>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>Lavinia</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -1022,13 +1035,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="15" customHeight="1" s="2">
+    <row r="28" ht="15" customHeight="1" s="5">
       <c r="A28" s="4" t="n">
         <v>27</v>
       </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Patrícia Gomes da Silva</t>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>Lilandra</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -1046,13 +1059,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="15" customHeight="1" s="2">
+    <row r="29" ht="15" customHeight="1" s="5">
       <c r="A29" s="4" t="n">
         <v>28</v>
       </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Paulo Henrique Araújo</t>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>Lilien</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -1070,13 +1083,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="15" customHeight="1" s="2">
+    <row r="30" ht="15" customHeight="1" s="5">
       <c r="A30" s="4" t="n">
         <v>29</v>
       </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Rafaela Martins Oliveira</t>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Lucas</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -1094,13 +1107,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="15" customHeight="1" s="2">
+    <row r="31" ht="15" customHeight="1" s="5">
       <c r="A31" s="4" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Rafael Eduardo Correia</t>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>Luisa</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
@@ -1118,13 +1131,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="15" customHeight="1" s="2">
+    <row r="32" ht="15" customHeight="1" s="5">
       <c r="A32" s="4" t="n">
         <v>31</v>
       </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Renata Carvalho Dias</t>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>Luiza</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -1142,13 +1155,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1" s="2">
+    <row r="33" ht="15" customHeight="1" s="5">
       <c r="A33" s="4" t="n">
         <v>32</v>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Ricardo Augusto Vieira</t>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>Manuela</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1166,13 +1179,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="15" customHeight="1" s="2">
+    <row r="34" ht="15" customHeight="1" s="5">
       <c r="A34" s="4" t="n">
         <v>33</v>
       </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Sabrina Mendes Souza</t>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Conhasca</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -1190,13 +1203,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="15" customHeight="1" s="2">
+    <row r="35" ht="15" customHeight="1" s="5">
       <c r="A35" s="4" t="n">
         <v>34</v>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Samuel Costa Ferreira</t>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Gomes</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -1214,13 +1227,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" ht="15" customHeight="1" s="2">
+    <row r="36" ht="15" customHeight="1" s="5">
       <c r="A36" s="4" t="n">
         <v>35</v>
       </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Sofia Rodrigues Almeida</t>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Ramos</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -1238,13 +1251,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" ht="15" customHeight="1" s="2">
+    <row r="37" ht="15" customHeight="1" s="5">
       <c r="A37" s="4" t="n">
         <v>36</v>
       </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Thiago Henrique Ramos</t>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>Maria Luisa</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -1262,13 +1275,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" ht="15" customHeight="1" s="2">
+    <row r="38" ht="15" customHeight="1" s="5">
       <c r="A38" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>Valentina Lopes Martins</t>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>Maria Luiza</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -1286,13 +1299,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" ht="15" customHeight="1" s="2">
+    <row r="39" ht="15" customHeight="1" s="5">
       <c r="A39" s="4" t="n">
         <v>38</v>
       </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>Victor Hugo Barbosa</t>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Marianna</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -1310,13 +1323,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" ht="15" customHeight="1" s="2">
+    <row r="40" ht="15" customHeight="1" s="5">
       <c r="A40" s="4" t="n">
         <v>39</v>
       </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>Vitória Gabriela Nunes</t>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>Mayara</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1334,13 +1347,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" ht="15" customHeight="1" s="2">
+    <row r="41" ht="15" customHeight="1" s="5">
       <c r="A41" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>William Fernandes Costa</t>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>Miguel</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1355,6 +1368,198 @@
         <v>1000</v>
       </c>
       <c r="G41" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="5">
+      <c r="A42" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Pedro Augusto</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>P41</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="5">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Pedro Henrique</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>P42</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="5">
+      <c r="A44" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>P43</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="5">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>Rafaela</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>P44</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="5">
+      <c r="A46" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>P45</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G46" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="5">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>Stella</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>P46</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="5">
+      <c r="A48" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>Vitoria</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>P47</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G48" s="4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="5">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Yuri</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>P48</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G49" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1371,42 +1576,54 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
+  <cols>
+    <col width="8.68" customWidth="1" style="4" min="1" max="1"/>
+    <col width="23.09" customWidth="1" style="4" min="2" max="2"/>
+    <col width="15.3" customWidth="1" style="4" min="3" max="3"/>
+    <col width="8.68" customWidth="1" style="4" min="4" max="6"/>
+    <col width="58" customWidth="1" style="4" min="7" max="7"/>
+  </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1" s="2">
-      <c r="A1" s="3" t="inlineStr">
+    <row r="1" ht="15" customHeight="1" s="5">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>Código</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>EDP</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>Etapa</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>Vendedor</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>Preço</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="15" customHeight="1" s="2">
+      <c r="G1" s="6" t="inlineStr">
+        <is>
+          <t>Fases influenciadas</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="15" customHeight="1" s="5">
       <c r="A2" s="4" t="inlineStr">
         <is>
           <t>P01</t>
@@ -1422,21 +1639,18 @@
           <t>Uso</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>Ana Beatriz Almeida</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="n">
-        <v>250</v>
-      </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>À venda</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1" s="2">
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1" s="5">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>P02</t>
@@ -1454,7 +1668,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Bruno Henrique Martins</t>
+          <t>Ana Clara</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
@@ -1465,8 +1679,13 @@
           <t>À venda</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="2">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="5">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>P03</t>
@@ -1482,43 +1701,53 @@
           <t>Uso</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>Camila Rodrigues Souza</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>900</v>
-      </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="15" customHeight="1" s="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>P04</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Facilitate maintenance</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Bianca Azevedo</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>250</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
           <t>À venda</t>
         </is>
       </c>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="2">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>P04</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Facilitate maintenance</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="2">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="15" customHeight="1" s="5">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>P05</t>
@@ -1536,19 +1765,24 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>Daniela Alves Ribeiro</t>
+          <t>Bianca Moraes</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
           <t>À venda</t>
         </is>
       </c>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="2">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1" s="5">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>P06</t>
@@ -1561,24 +1795,21 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Fim de vida</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>Diego Matheus Costa</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>300</v>
+          <t>Descarte</t>
+        </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>À venda</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="2">
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1" s="5">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>P07</t>
@@ -1591,24 +1822,21 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Fim de vida</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>Eduarda Lima Santos</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>250</v>
+          <t>Descarte</t>
+        </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>À venda</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="2">
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="5">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>P08</t>
@@ -1629,8 +1857,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="2">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="5">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>P09</t>
@@ -1643,7 +1876,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Extração / Materiais</t>
+          <t>Pré-produção / Materiais</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -1651,8 +1884,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="2">
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="15" customHeight="1" s="5">
       <c r="A11" s="4" t="inlineStr">
         <is>
           <t>P10</t>
@@ -1673,8 +1911,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="2">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>Produção, Pré-produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="5">
       <c r="A12" s="4" t="inlineStr">
         <is>
           <t>P11</t>
@@ -1687,552 +1930,669 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
+          <t>Distribuição</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="15" customHeight="1" s="5">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Minimize material consumption during usage (select more consumption-efficient systems)</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="5">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Minimize materials consumption during usage (engage systems with dynamic material consumption)</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="5">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Minimize energy consumption (during pre-production and production)</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
           <t>Produção</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Giovanna Pereira Lima</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>900</v>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>À venda</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="2">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>P12</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Minimize material consumption during usage (select more consumption-efficient systems)</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="2">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>P13</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>Minimize materials consumption during usage (engage systems with dynamic material consumption)</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="2">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>P14</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Minimize energy consumption (during pre-production and production)</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="5">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Minimize energy consumption (during transportation and storage)</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" s="5">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Minimize energy consumption (select systems with energy-efficient operation stage)</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="5">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Select non-toxic and harmless materials</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção / Materiais</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="5">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Select non-toxic and harmless energy resources</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção / Materiais</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="15" customHeight="1" s="5">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Select renewable and bio-compatible materials</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção / Materiais</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="5">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Select renewable and bio-compatible energy resources</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção / Materiais</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1" s="5">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>P21</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Adopt the cascade approach</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="15" customHeight="1" s="5">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Facilitate end-of-life collection and transportation</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="15" customHeight="1" s="5">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>P23</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Identify materials</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>Produção, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="5">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>P24</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Minimize the overall number of different incompatible materials</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="15" customHeight="1" s="5">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>P25</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Facilitate cleaning</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="5">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>P26</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Facilitate composting</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="15" customHeight="1" s="5">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>P27</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Reduce and facilitate operations of disassembly and separation</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="15" customHeight="1" s="5">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>P28</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Engage reversible joining systems</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="5">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>P29</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Develop services providing added value to the product’s life cycle</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="15" customHeight="1" s="5">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>P30</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Develop services providing ‘final results’</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="15" customHeight="1" s="5">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>P31</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Develop services providing ‘enabling platforms for customers’</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="5">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>P32</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Change raw material (low impact or recyclable/recycled)</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção / Materiais</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1" s="5">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>P33</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Modify raw material (reduce mass and volume)</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção / Materiais</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="15" customHeight="1" s="5">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>P34</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Use pre-manufactured material</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>Produção</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="2">
-      <c r="A16" s="4" t="inlineStr">
-        <is>
-          <t>P15</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="inlineStr">
-        <is>
-          <t>Minimize energy consumption (during transportation and storage)</t>
-        </is>
-      </c>
-      <c r="C16" s="4" t="inlineStr">
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="15" customHeight="1" s="5">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>P35</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Change material (low impact) for the packaging</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>Distribuição</t>
         </is>
       </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="2">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>P16</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Minimize energy consumption (select systems with energy-efficient operation stage)</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="2">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>P17</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>Select non-toxic and harmless materials</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="inlineStr">
-        <is>
-          <t>Extração / Materiais</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="2">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>P18</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Select non-toxic and harmless energy resources</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>Produção</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="2">
-      <c r="A20" s="4" t="inlineStr">
-        <is>
-          <t>P19</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="inlineStr">
-        <is>
-          <t>Select renewable and bio-compatible materials</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>Extração / Materiais</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="2">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>P20</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Select renewable and bio-compatible energy resources</t>
-        </is>
-      </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Produção</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="2">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>P21</t>
-        </is>
-      </c>
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>Adopt the cascade approach</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="inlineStr">
-        <is>
-          <t>Fim de vida</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="2">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>P22</t>
-        </is>
-      </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Facilitate end-of-life collection and transportation</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="inlineStr">
-        <is>
-          <t>Fim de vida</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="2">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>P23</t>
-        </is>
-      </c>
-      <c r="B24" s="4" t="inlineStr">
-        <is>
-          <t>Identify materials</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="inlineStr">
-        <is>
-          <t>Fim de vida</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="2">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>P24</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Minimize the overall number of different incompatible materials</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="inlineStr">
-        <is>
-          <t>Extração / Materiais</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="2">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>P25</t>
-        </is>
-      </c>
-      <c r="B26" s="4" t="inlineStr">
-        <is>
-          <t>Facilitate cleaning</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="2">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>P26</t>
-        </is>
-      </c>
-      <c r="B27" s="4" t="inlineStr">
-        <is>
-          <t>Facilitate composting</t>
-        </is>
-      </c>
-      <c r="C27" s="4" t="inlineStr">
-        <is>
-          <t>Fim de vida</t>
-        </is>
-      </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="2">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>P27</t>
-        </is>
-      </c>
-      <c r="B28" s="4" t="inlineStr">
-        <is>
-          <t>Reduce and facilitate operations of disassembly and separation</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="inlineStr">
-        <is>
-          <t>Fim de vida</t>
-        </is>
-      </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="2">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>P28</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Engage reversible joining systems</t>
-        </is>
-      </c>
-      <c r="C29" s="4" t="inlineStr">
-        <is>
-          <t>Produção</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="2">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>P29</t>
-        </is>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>Develop services providing added value to the product’s life cycle</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="2">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>P30</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Develop services providing ‘final results’</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="2">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>P31</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>Develop services providing ‘enabling platforms for customers’</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="2">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>P32</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Change raw material (low impact or recyclable/recycled)</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>Extração / Materiais</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="2">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>P33</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>Modify raw material (reduce mass and volume)</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>Extração / Materiais</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="2">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>P34</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Use pre-manufactured material</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>Produção</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Não anunciado</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="2">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>P35</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>Change material (low impact) for the packaging</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>Produção</t>
-        </is>
-      </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="2">
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="5">
       <c r="A37" s="4" t="inlineStr">
         <is>
           <t>P36</t>
@@ -2245,7 +2605,7 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Distribuição</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -2253,8 +2613,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="2">
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="15" customHeight="1" s="5">
       <c r="A38" s="4" t="inlineStr">
         <is>
           <t>P37</t>
@@ -2267,7 +2632,7 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Produção</t>
+          <t>Distribuição</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -2275,8 +2640,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="2">
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="15" customHeight="1" s="5">
       <c r="A39" s="4" t="inlineStr">
         <is>
           <t>P38</t>
@@ -2297,8 +2667,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="2">
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="5">
       <c r="A40" s="4" t="inlineStr">
         <is>
           <t>P39</t>
@@ -2319,8 +2694,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="2">
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="5">
       <c r="A41" s="4" t="inlineStr">
         <is>
           <t>P40</t>
@@ -2341,8 +2721,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="2">
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" s="5">
       <c r="A42" s="4" t="inlineStr">
         <is>
           <t>P41</t>
@@ -2363,8 +2748,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="43" ht="15" customHeight="1" s="2">
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="15" customHeight="1" s="5">
       <c r="A43" s="4" t="inlineStr">
         <is>
           <t>P42</t>
@@ -2385,8 +2775,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="15" customHeight="1" s="2">
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="5">
       <c r="A44" s="4" t="inlineStr">
         <is>
           <t>P43</t>
@@ -2407,8 +2802,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="45" ht="15" customHeight="1" s="2">
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="15" customHeight="1" s="5">
       <c r="A45" s="4" t="inlineStr">
         <is>
           <t>P44</t>
@@ -2429,8 +2829,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="15" customHeight="1" s="2">
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="5">
       <c r="A46" s="4" t="inlineStr">
         <is>
           <t>P45</t>
@@ -2451,8 +2856,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="47" ht="15" customHeight="1" s="2">
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="15" customHeight="1" s="5">
       <c r="A47" s="4" t="inlineStr">
         <is>
           <t>P46</t>
@@ -2473,8 +2883,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="15" customHeight="1" s="2">
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="5">
       <c r="A48" s="4" t="inlineStr">
         <is>
           <t>P47</t>
@@ -2495,8 +2910,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="49" ht="15" customHeight="1" s="2">
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="15" customHeight="1" s="5">
       <c r="A49" s="4" t="inlineStr">
         <is>
           <t>P48</t>
@@ -2517,8 +2937,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="50" ht="15" customHeight="1" s="2">
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="15" customHeight="1" s="5">
       <c r="A50" s="4" t="inlineStr">
         <is>
           <t>P49</t>
@@ -2539,8 +2964,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="51" ht="15" customHeight="1" s="2">
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="15" customHeight="1" s="5">
       <c r="A51" s="4" t="inlineStr">
         <is>
           <t>P50</t>
@@ -2553,7 +2983,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Uso</t>
+          <t>Distribuição</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -2561,8 +2991,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="52" ht="15" customHeight="1" s="2">
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="15" customHeight="1" s="5">
       <c r="A52" s="4" t="inlineStr">
         <is>
           <t>P51</t>
@@ -2583,8 +3018,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="53" ht="15" customHeight="1" s="2">
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="15" customHeight="1" s="5">
       <c r="A53" s="4" t="inlineStr">
         <is>
           <t>P52</t>
@@ -2605,8 +3045,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="54" ht="15" customHeight="1" s="2">
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="5">
       <c r="A54" s="4" t="inlineStr">
         <is>
           <t>P53</t>
@@ -2627,8 +3072,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="55" ht="15" customHeight="1" s="2">
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="15" customHeight="1" s="5">
       <c r="A55" s="4" t="inlineStr">
         <is>
           <t>P54</t>
@@ -2649,8 +3099,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="56" ht="15" customHeight="1" s="2">
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15" customHeight="1" s="5">
       <c r="A56" s="4" t="inlineStr">
         <is>
           <t>P55</t>
@@ -2671,8 +3126,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="57" ht="15" customHeight="1" s="2">
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15" customHeight="1" s="5">
       <c r="A57" s="4" t="inlineStr">
         <is>
           <t>P56</t>
@@ -2693,8 +3153,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="58" ht="15" customHeight="1" s="2">
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="5">
       <c r="A58" s="4" t="inlineStr">
         <is>
           <t>P57</t>
@@ -2715,8 +3180,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="59" ht="15" customHeight="1" s="2">
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="15" customHeight="1" s="5">
       <c r="A59" s="4" t="inlineStr">
         <is>
           <t>P58</t>
@@ -2737,8 +3207,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="60" ht="15" customHeight="1" s="2">
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Pré-produção, Produção, Distribuição, Uso, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15" customHeight="1" s="5">
       <c r="A60" s="4" t="inlineStr">
         <is>
           <t>P59</t>
@@ -2759,8 +3234,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="15" customHeight="1" s="2">
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15" customHeight="1" s="5">
       <c r="A61" s="4" t="inlineStr">
         <is>
           <t>P60</t>
@@ -2781,8 +3261,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="62" ht="15" customHeight="1" s="2">
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Uso</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15" customHeight="1" s="5">
       <c r="A62" s="4" t="inlineStr">
         <is>
           <t>P61</t>
@@ -2795,7 +3280,7 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Fim de vida</t>
+          <t>Descarte</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2803,8 +3288,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="63" ht="15" customHeight="1" s="2">
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="15" customHeight="1" s="5">
       <c r="A63" s="4" t="inlineStr">
         <is>
           <t>P62</t>
@@ -2817,7 +3307,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Fim de vida</t>
+          <t>Descarte</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2825,8 +3315,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="64" ht="15" customHeight="1" s="2">
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="15" customHeight="1" s="5">
       <c r="A64" s="4" t="inlineStr">
         <is>
           <t>P63</t>
@@ -2839,7 +3334,7 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Fim de vida</t>
+          <t>Descarte</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2847,8 +3342,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="65" ht="15" customHeight="1" s="2">
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15" customHeight="1" s="5">
       <c r="A65" s="4" t="inlineStr">
         <is>
           <t>P64</t>
@@ -2861,7 +3361,7 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Fim de vida</t>
+          <t>Descarte</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -2869,8 +3369,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="66" ht="15" customHeight="1" s="2">
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>Produção, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15" customHeight="1" s="5">
       <c r="A66" s="4" t="inlineStr">
         <is>
           <t>P65</t>
@@ -2883,7 +3388,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Fim de vida</t>
+          <t>Descarte</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -2891,8 +3396,13 @@
           <t>Não anunciado</t>
         </is>
       </c>
-    </row>
-    <row r="67" ht="15" customHeight="1" s="2">
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>Produção, Descarte</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15" customHeight="1" s="5">
       <c r="A67" s="4" t="inlineStr">
         <is>
           <t>P66</t>
@@ -2905,12 +3415,17 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Fim de vida</t>
+          <t>Descarte</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
           <t>Não anunciado</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>Distribuição, Descarte</t>
         </is>
       </c>
     </row>
@@ -2919,4 +3434,1992 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID compra</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Comprador ID</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Comprador</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Vendedor</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Código</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>EDP</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Etapa</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Preço</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Data/hora</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Caio</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>250</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bruna</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>250</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Bianca Azevedo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>250</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ana Julia</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>250</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Agnes</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>250</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ana Clara</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>250</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="n">
+        <v>9</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Caroline</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>250</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>11</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Erick</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>250</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>12</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Gabriella</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>250</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Giulia</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>250</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>14</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Guilherme</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>250</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>15</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Gustavo Felicio</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>250</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>16</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Gustavo Varela</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>250</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Igor</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>250</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>250</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>19</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Joao Batista</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>250</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Joao Paulo</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>250</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>21</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Joao Pedro</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>250</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>22</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>250</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>23</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Kassiane</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>250</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>24</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>250</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>25</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Laura</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>250</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>26</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Lavinia</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>250</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>27</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Lilandra</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>250</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>28</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Lilien</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>250</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="n">
+        <v>29</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>250</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="n">
+        <v>30</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Luisa</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>250</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="n">
+        <v>31</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Luiza</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>250</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="n">
+        <v>32</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Manuela</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>250</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="n">
+        <v>33</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Conhasca</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>250</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="n">
+        <v>34</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Gomes</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>250</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="n">
+        <v>35</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Ramos</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>250</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>36</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Maria Luisa</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>250</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="n">
+        <v>37</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Maria Luiza</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>250</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="n">
+        <v>38</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Marianna</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>250</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="n">
+        <v>39</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Mayara</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>250</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="n">
+        <v>40</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>250</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="n">
+        <v>41</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Pedro Augusto</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>250</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="n">
+        <v>42</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Pedro Henrique</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>250</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="n">
+        <v>43</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>250</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="n">
+        <v>44</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Rafaela</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>250</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="n">
+        <v>45</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>250</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="n">
+        <v>10</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>250</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="n">
+        <v>8</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Carolina</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>250</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="n">
+        <v>46</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Stella</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>250</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="n">
+        <v>47</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Vitoria</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>250</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="n">
+        <v>48</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Yuri</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Bianca Moraes</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>P05</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Facilitate repair</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Uso</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>250</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2026-10-01 16:31:28</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/EDP_MARKET.xlsx
+++ b/EDP_MARKET.xlsx
@@ -1607,9 +1607,10 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.68" customWidth="1" style="7" min="1" max="1"/>
-    <col width="23.09" customWidth="1" style="7" min="2" max="2"/>
+    <col width="30.74" customWidth="1" style="7" min="2" max="2"/>
     <col width="15.3" customWidth="1" style="7" min="3" max="3"/>
-    <col width="8.68" customWidth="1" style="7" min="4" max="6"/>
+    <col width="16.69" customWidth="1" style="7" min="4" max="4"/>
+    <col width="8.68" customWidth="1" style="7" min="5" max="6"/>
     <col width="58" customWidth="1" style="7" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -1666,9 +1667,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Agnes</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="n">
+        <v>100</v>
+      </c>
       <c r="F2" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G2" s="7" t="inlineStr">
@@ -1693,6 +1702,7 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D3" s="10" t="n"/>
       <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -1720,7 +1730,7 @@
           <t>Uso</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Ana Julia</t>
         </is>
@@ -1755,9 +1765,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Bianca Azevedo</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="n">
+        <v>100</v>
+      </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1782,6 +1800,7 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D6" s="10" t="n"/>
       <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -1809,9 +1828,17 @@
           <t>Descarte</t>
         </is>
       </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Bruna</t>
+        </is>
+      </c>
+      <c r="E7" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -1836,6 +1863,7 @@
           <t>Descarte</t>
         </is>
       </c>
+      <c r="D8" s="10" t="n"/>
       <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -1863,6 +1891,7 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D9" s="10" t="n"/>
       <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -1890,6 +1919,7 @@
           <t>Pré-produção / Materiais</t>
         </is>
       </c>
+      <c r="D10" s="10" t="n"/>
       <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -1917,9 +1947,17 @@
           <t>Produção</t>
         </is>
       </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Diego</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="n">
+        <v>400</v>
+      </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G11" s="7" t="inlineStr">
@@ -1944,9 +1982,17 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Erick</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -1971,9 +2017,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Gabriella</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -1998,9 +2052,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D14" s="10" t="inlineStr">
+        <is>
+          <t>Giulia</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G14" s="7" t="inlineStr">
@@ -2025,9 +2087,17 @@
           <t>Produção</t>
         </is>
       </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Guilherme</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G15" s="7" t="inlineStr">
@@ -2052,6 +2122,7 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D16" s="10" t="n"/>
       <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2079,9 +2150,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>Gustavo Varela</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="n">
+        <v>13</v>
+      </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G17" s="7" t="inlineStr">
@@ -2106,6 +2185,7 @@
           <t>Pré-produção / Materiais</t>
         </is>
       </c>
+      <c r="D18" s="10" t="n"/>
       <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2133,9 +2213,17 @@
           <t>Pré-produção / Materiais</t>
         </is>
       </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr">
@@ -2160,9 +2248,17 @@
           <t>Pré-produção / Materiais</t>
         </is>
       </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Joao Batista</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>120</v>
+      </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G20" s="7" t="inlineStr">
@@ -2187,9 +2283,17 @@
           <t>Pré-produção / Materiais</t>
         </is>
       </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Joao Paulo</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="n">
+        <v>300</v>
+      </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G21" s="7" t="inlineStr">
@@ -2214,9 +2318,17 @@
           <t>Descarte</t>
         </is>
       </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Joao Pedro</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr">
@@ -2241,9 +2353,17 @@
           <t>Descarte</t>
         </is>
       </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Jorge</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>250</v>
+      </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -2268,9 +2388,17 @@
           <t>Descarte</t>
         </is>
       </c>
+      <c r="D24" s="10" t="inlineStr">
+        <is>
+          <t>Kassiane</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="n">
+        <v>100</v>
+      </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G24" s="7" t="inlineStr">
@@ -2295,9 +2423,17 @@
           <t>Descarte</t>
         </is>
       </c>
+      <c r="D25" s="10" t="inlineStr">
+        <is>
+          <t>Larissa</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G25" s="7" t="inlineStr">
@@ -2322,6 +2458,7 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D26" s="10" t="n"/>
       <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2349,6 +2486,7 @@
           <t>Descarte</t>
         </is>
       </c>
+      <c r="D27" s="10" t="n"/>
       <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2376,6 +2514,7 @@
           <t>Descarte</t>
         </is>
       </c>
+      <c r="D28" s="10" t="n"/>
       <c r="F28" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2403,9 +2542,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Lilien</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G29" s="7" t="inlineStr">
@@ -2430,9 +2577,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Lucas</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="n">
+        <v>120</v>
+      </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G30" s="7" t="inlineStr">
@@ -2457,6 +2612,7 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D31" s="10" t="n"/>
       <c r="F31" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2484,6 +2640,7 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D32" s="10" t="n"/>
       <c r="F32" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2511,6 +2668,7 @@
           <t>Pré-produção / Materiais</t>
         </is>
       </c>
+      <c r="D33" s="10" t="n"/>
       <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2538,9 +2696,17 @@
           <t>Pré-produção / Materiais</t>
         </is>
       </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Conhasca</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G34" s="7" t="inlineStr">
@@ -2565,9 +2731,17 @@
           <t>Produção</t>
         </is>
       </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Gomes</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="n">
+        <v>200</v>
+      </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -2592,9 +2766,17 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D36" s="10" t="inlineStr">
+        <is>
+          <t>Maria Eduarda Ramos</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G36" s="7" t="inlineStr">
@@ -2619,6 +2801,7 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D37" s="10" t="n"/>
       <c r="F37" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2646,9 +2829,17 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>Maria Luiza</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>130</v>
+      </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G38" s="7" t="inlineStr">
@@ -2673,9 +2864,17 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>Marianna</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="n">
+        <v>50</v>
+      </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G39" s="7" t="inlineStr">
@@ -2700,6 +2899,7 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D40" s="10" t="n"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2727,9 +2927,17 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Miguel</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="n">
+        <v>40</v>
+      </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G41" s="7" t="inlineStr">
@@ -2754,9 +2962,17 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Pedro Augusto</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G42" s="7" t="inlineStr">
@@ -2781,9 +2997,17 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>Pedro Henrique</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="n">
+        <v>250</v>
+      </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G43" s="7" t="inlineStr">
@@ -2808,9 +3032,17 @@
           <t>Distribuição</t>
         </is>
       </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>Rafael</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>10</v>
+      </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G44" s="7" t="inlineStr">
@@ -2835,9 +3067,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>Rafaela</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="n">
+        <v>100</v>
+      </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G45" s="7" t="inlineStr">
@@ -2862,9 +3102,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Rodrigo</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>130</v>
+      </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G46" s="7" t="inlineStr">
@@ -2889,6 +3137,7 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D47" s="10" t="n"/>
       <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Não anunciado</t>
@@ -2916,9 +3165,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D48" s="10" t="inlineStr">
+        <is>
+          <t>Vitoria</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>150</v>
+      </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -2943,9 +3200,17 @@
           <t>Uso</t>
         </is>
       </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>Yuri</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="n">
+        <v>190</v>
+      </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>Não anunciado</t>
+          <t>À venda</t>
         </is>
       </c>
       <c r="G49" s="7" t="inlineStr">
@@ -3453,7 +3718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="8">
@@ -3503,494 +3768,54 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Agnes</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>120</v>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Bianca Azevedo</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>120</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" t="n">
-        <v>6</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bruna</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>120</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" t="n">
-        <v>8</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Carolina</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>120</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" t="n">
-        <v>10</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Diego</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>120</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>11</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Erick</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>120</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Gabriella</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>120</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" t="n">
-        <v>7</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Caio</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>120</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Bianca Moraes</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>120</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" t="n">
-        <v>9</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Caroline</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>120</v>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" t="n">
-        <v>13</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Giulia</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Ana Julia</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>P03</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Facilitate upgrading and adaptability</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Uso</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>120</v>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2026-10-06 10:54:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="1048529" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048530" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048531" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048532" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048533" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048534" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048535" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048536" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048537" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048538" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048539" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048540" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048541" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048542" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048543" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048544" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048545" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048546" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048547" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048548" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048549" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048550" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048551" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048552" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048553" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048554" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048555" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048556" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048557" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048558" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048559" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048560" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048561" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048562" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048563" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048564" ht="12.8" customHeight="1" s="8"/>
-    <row r="1048565" ht="12.8" customHeight="1" s="8"/>
+    <row r="1048518" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048519" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048520" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048521" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048522" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048523" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048524" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048525" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048526" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048527" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048528" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048529" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048530" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048531" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048532" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048533" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048534" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048535" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048536" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048537" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048538" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048539" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048540" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048541" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048542" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048543" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048544" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048545" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048546" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048547" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048548" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048549" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048550" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048551" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048552" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048553" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048554" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048555" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048556" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048557" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048558" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048559" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048560" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048561" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048562" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048563" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048564" ht="12.75" customHeight="1" s="8"/>
+    <row r="1048565" ht="12.75" customHeight="1" s="8"/>
     <row r="1048566" ht="12.8" customHeight="1" s="8"/>
     <row r="1048567" ht="12.8" customHeight="1" s="8"/>
     <row r="1048568" ht="12.8" customHeight="1" s="8"/>
@@ -4181,7 +4006,7 @@
         <v/>
       </c>
       <c r="H5" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" ht="23.25" customHeight="1" s="8">
@@ -4212,7 +4037,7 @@
         <v/>
       </c>
       <c r="H6" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1" s="8">
@@ -4243,7 +4068,7 @@
         <v/>
       </c>
       <c r="H7" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1" s="8">
@@ -4274,7 +4099,7 @@
         <v/>
       </c>
       <c r="H8" s="7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" ht="13.5" customHeight="1" s="8">
@@ -4429,7 +4254,7 @@
         <v/>
       </c>
       <c r="H13" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" ht="13.5" customHeight="1" s="8">
@@ -4460,7 +4285,7 @@
         <v/>
       </c>
       <c r="H14" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" ht="13.5" customHeight="1" s="8">
@@ -4491,7 +4316,7 @@
         <v/>
       </c>
       <c r="H15" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" ht="23.25" customHeight="1" s="8">
@@ -4584,7 +4409,7 @@
         <v/>
       </c>
       <c r="H18" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" ht="13.5" customHeight="1" s="8">
@@ -4677,7 +4502,7 @@
         <v/>
       </c>
       <c r="H21" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" ht="13.5" customHeight="1" s="8">
@@ -4708,7 +4533,7 @@
         <v/>
       </c>
       <c r="H22" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" ht="13.5" customHeight="1" s="8">
@@ -4739,7 +4564,7 @@
         <v/>
       </c>
       <c r="H23" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" ht="13.5" customHeight="1" s="8">
@@ -4770,7 +4595,7 @@
         <v/>
       </c>
       <c r="H24" s="7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25" ht="13.5" customHeight="1" s="8">
@@ -4801,7 +4626,7 @@
         <v/>
       </c>
       <c r="H25" s="7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26" ht="13.5" customHeight="1" s="8">
@@ -5080,7 +4905,7 @@
         <v/>
       </c>
       <c r="H34" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" ht="34.5" customHeight="1" s="8">
@@ -5204,7 +5029,7 @@
         <v/>
       </c>
       <c r="H38" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" ht="13.5" customHeight="1" s="8">
@@ -5235,7 +5060,7 @@
         <v/>
       </c>
       <c r="H39" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="13.5" customHeight="1" s="8">
@@ -5359,7 +5184,7 @@
         <v/>
       </c>
       <c r="H43" s="7" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" ht="13.5" customHeight="1" s="8">
@@ -5421,7 +5246,7 @@
         <v/>
       </c>
       <c r="H45" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" ht="13.5" customHeight="1" s="8">
@@ -5452,7 +5277,7 @@
         <v/>
       </c>
       <c r="H46" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" ht="13.5" customHeight="1" s="8">
@@ -5514,7 +5339,7 @@
         <v/>
       </c>
       <c r="H48" s="7" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" ht="13.5" customHeight="1" s="8">
@@ -5545,7 +5370,7 @@
         <v/>
       </c>
       <c r="H49" s="7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
